--- a/Test -Overseas Leave Application.xlsx
+++ b/Test -Overseas Leave Application.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kjtay\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kjtay\Desktop\Tanglin-ERT-OL-Calendar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07459CD-5FC6-403A-BC11-132E8CE724FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5304546A-64AA-4431-9D45-BEC00AAE19FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="J308" s="4" cm="1">
         <f t="array" ref="J308">MAX(COUNTIFS(Table1[Date of Departure], "&lt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]]), Table1[Date of Return], "&gt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]])))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K308" s="5" t="str">
         <f>IF(Table1[[#This Row],[Unit''s Leave Quota]]&lt;=6, "Approved", "Quota Exceeded")</f>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="J339" s="4" cm="1">
         <f t="array" ref="J339">MAX(COUNTIFS(Table1[Date of Departure], "&lt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]]), Table1[Date of Return], "&gt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]])))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K339" s="5" t="str">
         <f>IF(Table1[[#This Row],[Unit''s Leave Quota]]&lt;=6, "Approved", "Quota Exceeded")</f>
@@ -16689,7 +16689,7 @@
       </c>
       <c r="J351" s="4" cm="1">
         <f t="array" ref="J351">MAX(COUNTIFS(Table1[Date of Departure], "&lt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]]), Table1[Date of Return], "&gt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]])))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K351" s="5" t="str">
         <f>IF(Table1[[#This Row],[Unit''s Leave Quota]]&lt;=6, "Approved", "Quota Exceeded")</f>
@@ -17752,14 +17752,14 @@
         <v>46024</v>
       </c>
       <c r="H377" s="7">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="I377" s="5" t="s">
         <v>108</v>
       </c>
       <c r="J377" s="4" cm="1">
         <f t="array" ref="J377">MAX(COUNTIFS(Table1[Date of Departure], "&lt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]]), Table1[Date of Return], "&gt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]])))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K377" s="5" t="str">
         <f>IF(Table1[[#This Row],[Unit''s Leave Quota]]&lt;=6, "Approved", "Quota Exceeded")</f>
@@ -17795,14 +17795,14 @@
         <v>46024</v>
       </c>
       <c r="H378" s="7">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="I378" s="5" t="s">
         <v>108</v>
       </c>
       <c r="J378" s="4" cm="1">
         <f t="array" ref="J378">MAX(COUNTIFS(Table1[Date of Departure], "&lt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]]), Table1[Date of Return], "&gt;=" &amp; _xlfn.SEQUENCE(Table1[[#This Row],[Date of Return]] - Table1[[#This Row],[Date of Departure]] + 1, , Table1[[#This Row],[Date of Departure]])))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K378" s="5" t="str">
         <f>IF(Table1[[#This Row],[Unit''s Leave Quota]]&lt;=6, "Approved", "Quota Exceeded")</f>
@@ -18237,13 +18237,13 @@
         <v>46024</v>
       </c>
       <c r="H2" s="16">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="I2" t="str">
         <v>Marah Ishraf</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K2" t="str">
         <v>Approved</v>
@@ -18278,13 +18278,13 @@
         <v>46024</v>
       </c>
       <c r="H3" s="16">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="I3" t="str">
         <v>Marah Ishraf</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K3" t="str">
         <v>Approved</v>
@@ -18373,11 +18373,11 @@
       </c>
       <c r="B3">
         <f>COUNTIFS('2025'!G:G,"&lt;="&amp;A3,'2025'!H:H,"&gt;="&amp;A3)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" si="0">$G$1-B3</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="str">
         <f t="shared" ref="D3:D66" si="1">IF(C3&lt;0,"OVERBOOKED",IF(C3=0,"FULL","AVAILABLE"))</f>
@@ -18405,15 +18405,15 @@
       </c>
       <c r="B4">
         <f>COUNTIFS('2025'!G:G,"&lt;="&amp;A4,'2025'!H:H,"&gt;="&amp;A4)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" si="1"/>
-        <v>FULL</v>
+        <v>AVAILABLE</v>
       </c>
       <c r="E4" s="17" t="str" cm="1">
         <f t="array" ref="E4">IF(D4="OVERBOOKED",
@@ -28086,21 +28086,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C798F470B00F454C8CA677C63E6721D7" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="533dc311467df614029f34daead29ebf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="43a366e4-f98e-4004-a98b-325b777a1e5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d99918a1c9c3eded1d722a6b4572198" ns3:_="">
     <xsd:import namespace="43a366e4-f98e-4004-a98b-325b777a1e5e"/>
@@ -28244,24 +28229,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B416048F-EB34-4311-A6A2-24DA2F5F4752}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C49C5B3F-112D-4F0D-8572-47698068CDF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C97D7660-5665-4CC2-B407-391EBA4AEBD4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28277,4 +28260,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B416048F-EB34-4311-A6A2-24DA2F5F4752}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C49C5B3F-112D-4F0D-8572-47698068CDF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Test -Overseas Leave Application.xlsx
+++ b/Test -Overseas Leave Application.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kjtay\Desktop\Tanglin-ERT-OL-Calendar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5304546A-64AA-4431-9D45-BEC00AAE19FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFBAFE5-4D37-4E16-B394-F65E00772AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28086,6 +28086,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C798F470B00F454C8CA677C63E6721D7" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="533dc311467df614029f34daead29ebf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="43a366e4-f98e-4004-a98b-325b777a1e5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d99918a1c9c3eded1d722a6b4572198" ns3:_="">
     <xsd:import namespace="43a366e4-f98e-4004-a98b-325b777a1e5e"/>
@@ -28229,22 +28244,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C49C5B3F-112D-4F0D-8572-47698068CDF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B416048F-EB34-4311-A6A2-24DA2F5F4752}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C97D7660-5665-4CC2-B407-391EBA4AEBD4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28260,21 +28277,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B416048F-EB34-4311-A6A2-24DA2F5F4752}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C49C5B3F-112D-4F0D-8572-47698068CDF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>